--- a/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-8323_Simple_Rules_Ranges_Arrays.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-8323_Simple_Rules_Ranges_Arrays.xlsx
@@ -84,7 +84,7 @@
     <t>d</t>
   </si>
   <si>
-    <t>55,000.00</t>
+    <t>55000.00</t>
   </si>
   <si>
     <t>MMM\, FFF</t>
@@ -651,7 +651,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="1">
-        <v>7799</v>
+        <v>99</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
